--- a/ig/DM-MARS-2026/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -204,7 +204,7 @@
     <t>18</t>
   </si>
   <si>
-    <t>Intra-hospitalier</t>
+    <t>Intra-hospitalier (dont équipe de liaison)</t>
   </si>
   <si>
     <t>19</t>
